--- a/data/registered_fields.xlsx
+++ b/data/registered_fields.xlsx
@@ -2601,10 +2601,10 @@
     <t>LF06000</t>
   </si>
   <si>
-    <t>LF06006</t>
-  </si>
-  <si>
     <t>Salimon Z Banda</t>
+  </si>
+  <si>
+    <t>LF06005</t>
   </si>
 </sst>
 </file>
@@ -69859,13 +69859,13 @@
         <v>859</v>
       </c>
       <c r="B2132" t="s">
+        <v>861</v>
+      </c>
+      <c r="C2132" t="s">
         <v>860</v>
       </c>
-      <c r="C2132" t="s">
-        <v>861</v>
-      </c>
-      <c r="D2132">
-        <v>1.224</v>
+      <c r="D2132" s="2">
+        <v>1.78</v>
       </c>
       <c r="E2132" t="s">
         <v>50</v>
